--- a/artfynd/A 27607-2025 artfynd.xlsx
+++ b/artfynd/A 27607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126861821</v>
       </c>
       <c r="B2" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126861815</v>
       </c>
       <c r="B3" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126861801</v>
       </c>
       <c r="B4" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126861820</v>
       </c>
       <c r="B5" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126861803</v>
       </c>
       <c r="B6" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126861819</v>
       </c>
       <c r="B7" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126861822</v>
       </c>
       <c r="B8" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27607-2025 artfynd.xlsx
+++ b/artfynd/A 27607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126861821</v>
       </c>
       <c r="B2" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126861815</v>
       </c>
       <c r="B3" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126861801</v>
       </c>
       <c r="B4" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126861820</v>
       </c>
       <c r="B5" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126861803</v>
       </c>
       <c r="B6" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126861819</v>
       </c>
       <c r="B7" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126861822</v>
       </c>
       <c r="B8" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27607-2025 artfynd.xlsx
+++ b/artfynd/A 27607-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>126861801</v>
       </c>
       <c r="B4" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126861803</v>
       </c>
       <c r="B6" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 27607-2025 artfynd.xlsx
+++ b/artfynd/A 27607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126861821</v>
       </c>
       <c r="B2" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126861815</v>
       </c>
       <c r="B3" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126861801</v>
       </c>
       <c r="B4" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126861820</v>
       </c>
       <c r="B5" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126861803</v>
       </c>
       <c r="B6" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126861819</v>
       </c>
       <c r="B7" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126861822</v>
       </c>
       <c r="B8" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
